--- a/app/public/311_data.xlsx
+++ b/app/public/311_data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="武将表" sheetId="11" r:id="rId1"/>
@@ -2774,9 +2774,6 @@
     <t>citys</t>
   </si>
   <si>
-    <t xml:space="preserve"> color</t>
-  </si>
-  <si>
     <t>#ffe646</t>
   </si>
   <si>
@@ -2844,6 +2841,10 @@
   </si>
   <si>
     <t>长剑</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>color</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
@@ -32941,7 +32942,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="21" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B9" t="s">
         <v>77</v>
@@ -35543,7 +35544,7 @@
         <v>914</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>915</v>
+        <v>938</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="22.5" customHeight="1">
@@ -35557,7 +35558,7 @@
         <v>19</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="55.5" customHeight="1">
@@ -35568,10 +35569,10 @@
         <v>2</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>916</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>917</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>918</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="55.5" customHeight="1">
@@ -35582,10 +35583,10 @@
         <v>26</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>918</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>919</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>920</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="39" customHeight="1">
@@ -35596,10 +35597,10 @@
         <v>4</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>920</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>921</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>922</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="39" customHeight="1">
@@ -35610,10 +35611,10 @@
         <v>46</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>922</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>923</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>924</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="55.5" customHeight="1">
@@ -35624,10 +35625,10 @@
         <v>138</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>924</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>925</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>926</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="39" customHeight="1">
@@ -35638,10 +35639,10 @@
         <v>22</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>926</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>927</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>928</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="55.5" customHeight="1">
@@ -35652,10 +35653,10 @@
         <v>17</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>928</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>929</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>930</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="22.5" customHeight="1">
@@ -35669,7 +35670,7 @@
         <v>47</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="22.5" customHeight="1">
@@ -35683,7 +35684,7 @@
         <v>30</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="22.5" customHeight="1">
@@ -35694,10 +35695,10 @@
         <v>166</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>932</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>933</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>934</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="22.5" customHeight="1">
@@ -35711,7 +35712,7 @@
         <v>134</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="22.5" customHeight="1">
@@ -35725,7 +35726,7 @@
         <v>197</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="55.5" customHeight="1">
@@ -35736,10 +35737,10 @@
         <v>159</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>935</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>936</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>937</v>
       </c>
     </row>
   </sheetData>

--- a/app/public/311_data.xlsx
+++ b/app/public/311_data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="武将表" sheetId="11" r:id="rId1"/>
@@ -2288,12 +2288,6 @@
     <t>纶巾</t>
   </si>
   <si>
-    <t>ownerId</t>
-  </si>
-  <si>
-    <t>lordId</t>
-  </si>
-  <si>
     <t>tong</t>
   </si>
   <si>
@@ -2316,9 +2310,6 @@
   </si>
   <si>
     <t>liang</t>
-  </si>
-  <si>
-    <t>position_x</t>
   </si>
   <si>
     <t>position_y</t>
@@ -2845,6 +2836,18 @@
   </si>
   <si>
     <t>color</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>position_x</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>ownerId</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>lordId</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
@@ -32942,7 +32945,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="21" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="B9" t="s">
         <v>77</v>
@@ -33044,45 +33047,45 @@
         <v>731</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>937</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>938</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>753</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>754</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>755</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>756</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>757</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>758</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>760</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
+        <v>936</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>761</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>762</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>763</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>764</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="22.5" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>25</v>
@@ -33126,7 +33129,7 @@
     </row>
     <row r="3" spans="1:14" ht="22.5" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>514</v>
@@ -33170,10 +33173,10 @@
     </row>
     <row r="4" spans="1:14" ht="22.5" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="C4" s="2">
         <v>0</v>
@@ -33214,7 +33217,7 @@
     </row>
     <row r="5" spans="1:14" ht="22.5" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>442</v>
@@ -33258,7 +33261,7 @@
     </row>
     <row r="6" spans="1:14" ht="22.5" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>275</v>
@@ -33302,7 +33305,7 @@
     </row>
     <row r="7" spans="1:14" ht="22.5" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>91</v>
@@ -33346,7 +33349,7 @@
     </row>
     <row r="8" spans="1:14" ht="22.5" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>64</v>
@@ -33390,7 +33393,7 @@
     </row>
     <row r="9" spans="1:14" ht="22.5" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>71</v>
@@ -33434,7 +33437,7 @@
     </row>
     <row r="10" spans="1:14" ht="22.5" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>36</v>
@@ -33478,7 +33481,7 @@
     </row>
     <row r="11" spans="1:14" ht="22.5" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>47</v>
@@ -33522,7 +33525,7 @@
     </row>
     <row r="12" spans="1:14" ht="22.5" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>32</v>
@@ -33566,7 +33569,7 @@
     </row>
     <row r="13" spans="1:14" ht="22.5" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>30</v>
@@ -33610,7 +33613,7 @@
     </row>
     <row r="14" spans="1:14" ht="22.5" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>81</v>
@@ -33654,7 +33657,7 @@
     </row>
     <row r="15" spans="1:14" ht="22.5" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>137</v>
@@ -33698,7 +33701,7 @@
     </row>
     <row r="16" spans="1:14" ht="22.5" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>62</v>
@@ -33742,7 +33745,7 @@
     </row>
     <row r="17" spans="1:14" ht="22.5" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>382</v>
@@ -33786,7 +33789,7 @@
     </row>
     <row r="18" spans="1:14" ht="22.5" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>15</v>
@@ -33830,7 +33833,7 @@
     </row>
     <row r="19" spans="1:14" ht="22.5" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>243</v>
@@ -33874,7 +33877,7 @@
     </row>
     <row r="20" spans="1:14" ht="22.5" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>301</v>
@@ -33918,7 +33921,7 @@
     </row>
     <row r="21" spans="1:14" ht="22.5" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>159</v>
@@ -33962,7 +33965,7 @@
     </row>
     <row r="22" spans="1:14" ht="22.5" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>340</v>
@@ -34006,7 +34009,7 @@
     </row>
     <row r="23" spans="1:14" ht="22.5" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>23</v>
@@ -34050,7 +34053,7 @@
     </row>
     <row r="24" spans="1:14" ht="22.5" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>96</v>
@@ -34094,7 +34097,7 @@
     </row>
     <row r="25" spans="1:14" ht="22.5" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>19</v>
@@ -34138,7 +34141,7 @@
     </row>
     <row r="26" spans="1:14" ht="22.5" customHeight="1">
       <c r="A26" s="5" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>432</v>
@@ -34182,7 +34185,7 @@
     </row>
     <row r="27" spans="1:14" ht="22.5" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>21</v>
@@ -34226,7 +34229,7 @@
     </row>
     <row r="28" spans="1:14" ht="22.5" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>28</v>
@@ -34270,7 +34273,7 @@
     </row>
     <row r="29" spans="1:14" ht="22.5" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>368</v>
@@ -34314,7 +34317,7 @@
     </row>
     <row r="30" spans="1:14" ht="22.5" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>60</v>
@@ -34358,7 +34361,7 @@
     </row>
     <row r="31" spans="1:14" ht="39" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>54</v>
@@ -34402,7 +34405,7 @@
     </row>
     <row r="32" spans="1:14" ht="22.5" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>87</v>
@@ -34446,7 +34449,7 @@
     </row>
     <row r="33" spans="1:14" ht="22.5" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>104</v>
@@ -34490,7 +34493,7 @@
     </row>
     <row r="34" spans="1:14" ht="22.5" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>114</v>
@@ -34534,7 +34537,7 @@
     </row>
     <row r="35" spans="1:14" ht="22.5" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>360</v>
@@ -34578,7 +34581,7 @@
     </row>
     <row r="36" spans="1:14" ht="22.5" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>75</v>
@@ -34622,7 +34625,7 @@
     </row>
     <row r="37" spans="1:14" ht="22.5" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>134</v>
@@ -34666,7 +34669,7 @@
     </row>
     <row r="38" spans="1:14" ht="22.5" customHeight="1">
       <c r="A38" s="2" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>34</v>
@@ -34710,7 +34713,7 @@
     </row>
     <row r="39" spans="1:14" ht="22.5" customHeight="1">
       <c r="A39" s="2" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>197</v>
@@ -34754,7 +34757,7 @@
     </row>
     <row r="40" spans="1:14" ht="22.5" customHeight="1">
       <c r="A40" s="2" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>362</v>
@@ -34798,7 +34801,7 @@
     </row>
     <row r="41" spans="1:14" ht="22.5" customHeight="1">
       <c r="A41" s="2" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>42</v>
@@ -34842,7 +34845,7 @@
     </row>
     <row r="42" spans="1:14" ht="22.5" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>481</v>
@@ -34886,7 +34889,7 @@
     </row>
     <row r="43" spans="1:14" ht="22.5" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>58</v>
@@ -34952,568 +34955,568 @@
         <v>731</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="22.5" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="22.5" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="22.5" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="22.5" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="22.5" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="22.5" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="22.5" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="22.5" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="22.5" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="22.5" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="22.5" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="22.5" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="22.5" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="22.5" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="22.5" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="22.5" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="22.5" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="22.5" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="22.5" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="22.5" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="22.5" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="22.5" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="22.5" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="22.5" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="22.5" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>885</v>
+        <v>882</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="22.5" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="22.5" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="22.5" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>888</v>
+        <v>885</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="22.5" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="22.5" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="22.5" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="22.5" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="22.5" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="22.5" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="22.5" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="22.5" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="22.5" customHeight="1">
       <c r="A38" s="2" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>897</v>
+        <v>894</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="22.5" customHeight="1">
       <c r="A39" s="2" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="22.5" customHeight="1">
       <c r="A40" s="2" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="22.5" customHeight="1">
       <c r="A41" s="2" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="22.5" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="22.5" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="22.5" customHeight="1">
       <c r="A44" s="2" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="22.5" customHeight="1">
       <c r="A45" s="2" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="22.5" customHeight="1">
       <c r="A46" s="2" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>906</v>
+        <v>903</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="22.5" customHeight="1">
       <c r="A47" s="2" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="22.5" customHeight="1">
       <c r="A48" s="2" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="22.5" customHeight="1">
       <c r="A49" s="2" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="22.5" customHeight="1">
       <c r="A50" s="2" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="22.5" customHeight="1">
       <c r="A51" s="2" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="22.5" customHeight="1">
       <c r="A52" s="2" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
     </row>
   </sheetData>
@@ -35541,10 +35544,10 @@
         <v>731</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="22.5" customHeight="1">
@@ -35558,7 +35561,7 @@
         <v>19</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="55.5" customHeight="1">
@@ -35569,10 +35572,10 @@
         <v>2</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="55.5" customHeight="1">
@@ -35583,10 +35586,10 @@
         <v>26</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>918</v>
+        <v>915</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="39" customHeight="1">
@@ -35597,10 +35600,10 @@
         <v>4</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>921</v>
+        <v>918</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="39" customHeight="1">
@@ -35611,10 +35614,10 @@
         <v>46</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="55.5" customHeight="1">
@@ -35625,10 +35628,10 @@
         <v>138</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="39" customHeight="1">
@@ -35639,10 +35642,10 @@
         <v>22</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="55.5" customHeight="1">
@@ -35653,10 +35656,10 @@
         <v>17</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="22.5" customHeight="1">
@@ -35670,7 +35673,7 @@
         <v>47</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="22.5" customHeight="1">
@@ -35684,7 +35687,7 @@
         <v>30</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="22.5" customHeight="1">
@@ -35695,10 +35698,10 @@
         <v>166</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="22.5" customHeight="1">
@@ -35712,7 +35715,7 @@
         <v>134</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="22.5" customHeight="1">
@@ -35726,7 +35729,7 @@
         <v>197</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="55.5" customHeight="1">
@@ -35737,10 +35740,10 @@
         <v>159</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
     </row>
   </sheetData>

--- a/app/public/311_data.xlsx
+++ b/app/public/311_data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" activeTab="3"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="武将表" sheetId="11" r:id="rId1"/>

--- a/app/public/311_data.xlsx
+++ b/app/public/311_data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="武将表" sheetId="11" r:id="rId1"/>
